--- a/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>14,32; 21,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>20,58; 29,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>24,04; 33,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>40,37; 57,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>49,01; 58,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>52,86; 62,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>58,94; 68,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>59,96; 74,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>32,17; 38,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>37,39; 43,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>42,5; 49,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>51,59; 63,15</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>38,55; 46,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>46,39; 54,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>55,03; 63,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>61,95; 73,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>83,25; 88,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>85,32; 90,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>85,73; 90,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>90,53; 96,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>59,93; 64,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>65,22; 70,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>71,1; 75,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>77,94; 86,15</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>37,06; 44,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>53,29; 60,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>62,97; 70,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>73,35; 80,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>90,69; 94,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>92,05; 95,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>94,2; 97,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>96,15; 98,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>65,61; 70,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>73,64; 78,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>79,26; 83,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>85,6; 90,09</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>29,61; 38,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>44,31; 53,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>55,56; 63,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>22,16; 73,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>91,76; 96,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>91,12; 95,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>93,37; 96,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>96,21; 98,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>60,72; 66,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>68,41; 73,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>74,84; 79,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>47,49; 86,38</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>21,07; 30,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>33,26; 43,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>46,22; 55,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>65,47; 72,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>92,13; 96,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>86,82; 93,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>93,35; 97,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>95,65; 97,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>57,28; 63,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>61,56; 68,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>70,53; 76,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>80,45; 84,58</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>34,23; 45,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>30,52; 41,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>40,93; 51,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>58,75; 67,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>86,13; 92,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>83,45; 90,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>89,61; 95,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>94,11; 98,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>62,85; 70,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>59,56; 67,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>67,82; 74,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>78,75; 91,96</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>29,21; 42,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>24,0; 36,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>32,44; 43,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>44,51; 53,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>64,82; 75,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>53,8; 63,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>61,65; 72,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>71,55; 77,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>52,61; 61,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>43,93; 52,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>51,96; 60,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>61,85; 67,35</t>
         </is>
       </c>
     </row>
@@ -1629,62 +1629,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>32,51; 35,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>41,96; 45,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>51,22; 54,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>46,73; 66,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,71; 85,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,28; 84,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>86,21; 88,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,04</t>
+          <t>90,37; 93,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>58,32; 60,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>62,82; 65,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>69,55; 71,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,02</t>
+          <t>68,12; 80,32</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1932,62 +1932,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
     </row>
@@ -2000,62 +2000,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86388</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110204</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>196451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249931</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248296</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>251776</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211927</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336319</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358500</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>372764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408377</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>70750; 104965</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>93485; 131884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>100401; 139720</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>161492; 231365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>228690; 271716</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>227399; 268075</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>233245; 270509</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2889</t>
+          <t>187793; 234205</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>309057; 367996</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1956</t>
+          <t>330708; 386711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>345712; 400278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3603</t>
+          <t>367899; 450402</t>
         </is>
       </c>
     </row>
@@ -2140,62 +2140,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>287</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>792</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>636</t>
         </is>
       </c>
     </row>
@@ -2208,62 +2208,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310966</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>343903</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>536640</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>538023</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>498155</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479432</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>847605</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>849022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>765367</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>283556; 338691</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1975</t>
+          <t>318739; 371342</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>324957; 373769</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2683</t>
+          <t>262396; 310726</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2027</t>
+          <t>518488; 553619</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>520681; 553052</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1866</t>
+          <t>482343; 511013</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2128</t>
+          <t>463617; 492918</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>814023; 881947</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>846079; 916768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1932</t>
+          <t>819829; 876112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2352</t>
+          <t>729196; 806067</t>
         </is>
       </c>
     </row>
@@ -2348,62 +2348,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>372</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>639</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>823</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1236</t>
         </is>
       </c>
     </row>
@@ -2416,62 +2416,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>262009</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>389913</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>446550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642419</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>668701</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634162</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>576164</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>904428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1058615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1080711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989500</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>236362; 286836</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2008</t>
+          <t>363372; 415449</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>419617; 470189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>393380; 433318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2010</t>
+          <t>625506; 653571</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>653391; 679576</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>622140; 643927</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1339</t>
+          <t>569197; 582220</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>871021; 941507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>1024866; 1089492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1959</t>
+          <t>1051638; 1108359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1553</t>
+          <t>965844; 1016498</t>
         </is>
       </c>
     </row>
@@ -2556,62 +2556,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>505</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>627</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1596</t>
         </is>
       </c>
     </row>
@@ -2624,62 +2624,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172244</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299437</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>468927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>486010</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>575383</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617596</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>693913</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>658253</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1162839</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2055</t>
+          <t>153718; 197461</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2149</t>
+          <t>272329; 328007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2126</t>
+          <t>357405; 408545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2560</t>
+          <t>196737; 656396</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>473131; 495471</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2191</t>
+          <t>561485; 587766</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>605052; 627016</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1199</t>
+          <t>685192; 699957</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>628329; 691775</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2172</t>
+          <t>841972; 910029</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>966478; 1029930</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1701</t>
+          <t>759757; 1382062</t>
         </is>
       </c>
     </row>
@@ -2764,62 +2764,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>373</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>974</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>470</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1429</t>
         </is>
       </c>
     </row>
@@ -2832,62 +2832,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98100</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164122</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386377</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>381069</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403077</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>473098</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>531277</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479169</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>567200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>717261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>917654</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1889</t>
+          <t>81486; 116356</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>142469; 185517</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2159</t>
+          <t>220913; 266737</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1623</t>
+          <t>367447; 408419</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1953</t>
+          <t>371273; 388896</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>388773; 416657</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2198</t>
+          <t>462800; 481178</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1049</t>
+          <t>524057; 536275</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>452302; 503789</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2106</t>
+          <t>539341; 596625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2182</t>
+          <t>686730; 743026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 1279</t>
+          <t>892336; 938071</t>
         </is>
       </c>
     </row>
@@ -2972,62 +2972,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>780</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1137</t>
         </is>
       </c>
     </row>
@@ -3040,62 +3040,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116236</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111894</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307160</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308545</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>349523</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>586226</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>423396</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>420438</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>504792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>816720</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1847</t>
+          <t>100145; 133813</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2101</t>
+          <t>94555; 130059</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>136425; 172399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1239</t>
+          <t>215662; 245997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>295374; 316731</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>294586; 320490</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>337657; 358121</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1411</t>
+          <t>572028; 599535</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1808</t>
+          <t>399452; 446463</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>394746; 445963</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>481552; 528564</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1342</t>
+          <t>767722; 896448</t>
         </is>
       </c>
     </row>
@@ -3180,62 +3180,62 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>666</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>892</t>
         </is>
       </c>
     </row>
@@ -3248,62 +3248,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74394</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76369</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234057</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228795</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269057</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318639</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308451</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>367134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>457728</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1822</t>
+          <t>61301; 88425</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>59955; 92019</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1629</t>
+          <t>83120; 111525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1183</t>
+          <t>125844; 151896</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2202</t>
+          <t>216445; 251653</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2127</t>
+          <t>209290; 247960</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2543</t>
+          <t>246712; 291810</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 927</t>
+          <t>304700; 331225</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>286101; 333948</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2141</t>
+          <t>280658; 334460</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>341061; 394782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 1016</t>
+          <t>438262; 477248</t>
         </is>
       </c>
     </row>
@@ -3388,62 +3388,62 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7164</t>
         </is>
       </c>
     </row>
@@ -3456,62 +3456,62 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1120336</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1495841</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1798474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2120608</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2837285</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2970821</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3093366</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3397577</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3957622</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4466662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4891842</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5518185</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>1064943; 1177799</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>1437310; 1559799</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>1734100; 1856067</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>1616269; 2302431</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>2791090; 2877241</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>2926098; 3019903</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>3051482; 3135285</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>3353826; 3455773</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>3878149; 4043597</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>4386140; 4552176</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>4816483; 4963963</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 1576</t>
+          <t>4883769; 5758566</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 21,25</t>
+          <t>14,08; 21,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,58; 29,04</t>
+          <t>20,54; 28,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,04; 33,46</t>
+          <t>24,56; 33,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,37; 57,84</t>
+          <t>40,36; 56,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,23</t>
+          <t>49,08; 57,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,86; 62,31</t>
+          <t>53,1; 62,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,94; 68,35</t>
+          <t>58,5; 68,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,96; 74,78</t>
+          <t>60,71; 74,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 38,31</t>
+          <t>32,09; 38,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,39; 43,73</t>
+          <t>37,17; 43,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,5; 49,21</t>
+          <t>42,4; 49,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,59; 63,15</t>
+          <t>52,71; 64,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,55; 46,05</t>
+          <t>38,44; 45,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,39; 54,05</t>
+          <t>46,32; 53,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,03; 63,3</t>
+          <t>55,44; 63,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,95; 73,36</t>
+          <t>59,55; 71,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,25; 88,89</t>
+          <t>83,36; 88,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,32; 90,63</t>
+          <t>85,29; 90,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,73; 90,83</t>
+          <t>85,88; 91,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,53; 96,26</t>
+          <t>89,19; 95,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,93; 64,93</t>
+          <t>59,51; 65,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,22; 70,67</t>
+          <t>65,2; 70,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,1; 75,98</t>
+          <t>70,92; 75,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,94; 86,15</t>
+          <t>75,92; 82,52</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,06; 44,97</t>
+          <t>36,97; 44,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,29; 60,93</t>
+          <t>53,04; 60,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,97; 70,56</t>
+          <t>63,17; 70,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,79</t>
+          <t>71,36; 79,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,69; 94,76</t>
+          <t>90,97; 94,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,05; 95,74</t>
+          <t>91,94; 95,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,2; 97,5</t>
+          <t>94,32; 97,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,15; 98,35</t>
+          <t>95,71; 98,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,61; 70,92</t>
+          <t>65,57; 70,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,64; 78,28</t>
+          <t>73,84; 78,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79,26; 83,53</t>
+          <t>79,23; 83,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,6; 90,09</t>
+          <t>84,18; 88,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,61; 38,04</t>
+          <t>28,84; 37,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,31; 53,37</t>
+          <t>44,31; 53,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,56; 63,5</t>
+          <t>55,77; 63,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 73,94</t>
+          <t>68,78; 75,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,76; 96,09</t>
+          <t>91,71; 96,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,12; 95,39</t>
+          <t>90,67; 95,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,37; 96,76</t>
+          <t>93,5; 96,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96,21; 98,28</t>
+          <t>96,2; 98,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,72; 66,85</t>
+          <t>60,42; 66,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68,41; 73,94</t>
+          <t>67,87; 73,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,84; 79,75</t>
+          <t>74,94; 79,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,49; 86,38</t>
+          <t>83,3; 86,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,07; 30,09</t>
+          <t>21,32; 30,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,26; 43,31</t>
+          <t>33,42; 43,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,22; 55,81</t>
+          <t>46,36; 56,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,47; 72,77</t>
+          <t>65,4; 72,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,13; 96,51</t>
+          <t>91,75; 96,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,82; 93,05</t>
+          <t>86,87; 92,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,35; 97,06</t>
+          <t>92,81; 97,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,65; 97,88</t>
+          <t>95,71; 97,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,28; 63,8</t>
+          <t>57,15; 64,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,56; 68,09</t>
+          <t>61,47; 68,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,53; 76,31</t>
+          <t>70,47; 76,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,45; 84,58</t>
+          <t>80,76; 84,64</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,23; 45,73</t>
+          <t>34,05; 45,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,52; 41,98</t>
+          <t>30,4; 41,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,93; 51,73</t>
+          <t>40,51; 51,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58,75; 67,02</t>
+          <t>58,11; 66,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,13; 92,36</t>
+          <t>86,4; 92,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83,45; 90,79</t>
+          <t>83,84; 91,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,61; 95,04</t>
+          <t>89,94; 94,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94,11; 98,64</t>
+          <t>92,39; 95,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,85; 70,25</t>
+          <t>62,92; 70,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59,56; 67,29</t>
+          <t>59,84; 67,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67,82; 74,44</t>
+          <t>67,55; 74,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78,75; 91,96</t>
+          <t>76,52; 81,14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,21; 42,13</t>
+          <t>28,74; 41,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,0; 36,83</t>
+          <t>24,85; 36,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,44; 43,52</t>
+          <t>32,82; 43,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,51; 53,72</t>
+          <t>44,35; 53,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,82; 75,37</t>
+          <t>64,59; 75,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,8; 63,75</t>
+          <t>53,49; 64,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,65; 72,92</t>
+          <t>61,81; 72,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,55; 77,78</t>
+          <t>71,9; 77,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52,61; 61,41</t>
+          <t>52,06; 61,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,93; 52,36</t>
+          <t>43,84; 52,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51,96; 60,14</t>
+          <t>51,84; 59,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,85; 67,35</t>
+          <t>61,52; 67,07</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,51; 35,96</t>
+          <t>32,5; 35,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,96; 45,53</t>
+          <t>41,96; 45,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51,22; 54,83</t>
+          <t>51,19; 54,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46,73; 66,57</t>
+          <t>63,75; 67,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>82,71; 85,26</t>
+          <t>82,87; 85,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,28; 84,92</t>
+          <t>82,2; 84,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,21; 88,58</t>
+          <t>86,31; 88,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,37; 93,12</t>
+          <t>89,56; 91,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,32; 60,8</t>
+          <t>58,33; 60,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62,82; 65,2</t>
+          <t>62,81; 65,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,68</t>
+          <t>69,58; 71,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,12; 80,32</t>
+          <t>77,31; 79,47</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>211927</t>
+          <t>247501</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>408377</t>
+          <t>446798</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70750; 104965</t>
+          <t>69558; 103830</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93485; 131884</t>
+          <t>93289; 130313</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100401; 139720</t>
+          <t>102560; 139831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161492; 231365</t>
+          <t>164597; 230305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>228690; 271716</t>
+          <t>228998; 269968</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>227399; 268075</t>
+          <t>228447; 267840</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>233245; 270509</t>
+          <t>231499; 269316</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>187793; 234205</t>
+          <t>220076; 270228</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>309057; 367996</t>
+          <t>308246; 370182</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>330708; 386711</t>
+          <t>328718; 387950</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>345712; 400278</t>
+          <t>344874; 400128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>367899; 450402</t>
+          <t>406066; 493800</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285935</t>
+          <t>313266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>479432</t>
+          <t>465725</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>765367</t>
+          <t>778991</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>283556; 338691</t>
+          <t>282733; 337016</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>318739; 371342</t>
+          <t>318274; 370402</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>324957; 373769</t>
+          <t>327359; 374406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>262396; 310726</t>
+          <t>283993; 339440</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>518488; 553619</t>
+          <t>519169; 552308</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>520681; 553052</t>
+          <t>520484; 554194</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>482343; 511013</t>
+          <t>483150; 512083</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>463617; 492918</t>
+          <t>447471; 477102</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>814023; 881947</t>
+          <t>808328; 883563</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>846079; 916768</t>
+          <t>845812; 915702</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>819829; 876112</t>
+          <t>817835; 875687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>729196; 806067</t>
+          <t>743018; 807527</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413336</t>
+          <t>468248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>576164</t>
+          <t>604805</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>989500</t>
+          <t>1073052</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>236362; 286836</t>
+          <t>235810; 286223</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>363372; 415449</t>
+          <t>361668; 415607</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>419617; 470189</t>
+          <t>420994; 469974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393380; 433318</t>
+          <t>443059; 490534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>625506; 653571</t>
+          <t>627447; 654922</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>653391; 679576</t>
+          <t>652665; 680013</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>622140; 643927</t>
+          <t>622966; 643702</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>569197; 582220</t>
+          <t>596453; 610883</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>871021; 941507</t>
+          <t>870432; 940778</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1024866; 1089492</t>
+          <t>1027700; 1089292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1051638; 1108359</t>
+          <t>1051202; 1107794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>965844; 1016498</t>
+          <t>1047200; 1096373</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>468927</t>
+          <t>507007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>693913</t>
+          <t>716572</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1162839</t>
+          <t>1223579</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>153718; 197461</t>
+          <t>149740; 195615</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>272329; 328007</t>
+          <t>272362; 325818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>357405; 408545</t>
+          <t>358815; 409823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>196737; 656396</t>
+          <t>481908; 531551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>473131; 495471</t>
+          <t>472916; 495788</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>561485; 587766</t>
+          <t>558725; 586776</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>605052; 627016</t>
+          <t>605922; 628071</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>685192; 699957</t>
+          <t>708240; 722718</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>628329; 691775</t>
+          <t>625188; 692263</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>841972; 910029</t>
+          <t>835368; 909837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>966478; 1029930</t>
+          <t>967721; 1028891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>759757; 1382062</t>
+          <t>1196863; 1248688</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386377</t>
+          <t>418530</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>531277</t>
+          <t>590445</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>917654</t>
+          <t>1008976</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81486; 116356</t>
+          <t>82455; 116316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>142469; 185517</t>
+          <t>143156; 184321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220913; 266737</t>
+          <t>221544; 267693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>367447; 408419</t>
+          <t>398525; 441204</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>371273; 388896</t>
+          <t>369737; 388616</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>388773; 416657</t>
+          <t>388985; 416159</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>462800; 481178</t>
+          <t>460085; 480968</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>524057; 536275</t>
+          <t>582729; 596311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>452302; 503789</t>
+          <t>451278; 506384</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>539341; 596625</t>
+          <t>538588; 596664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>686730; 743026</t>
+          <t>686148; 743517</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>892336; 938071</t>
+          <t>983837; 1031072</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230492</t>
+          <t>253943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>586226</t>
+          <t>413444</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>816720</t>
+          <t>667387</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100145; 133813</t>
+          <t>99619; 133370</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94555; 130059</t>
+          <t>94182; 129192</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>136425; 172399</t>
+          <t>135014; 171761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>215662; 245997</t>
+          <t>235926; 270386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>295374; 316731</t>
+          <t>296308; 317564</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>294586; 320490</t>
+          <t>295948; 321231</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>337657; 358121</t>
+          <t>338893; 357913</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>572028; 599535</t>
+          <t>405232; 420071</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>399452; 446463</t>
+          <t>399841; 445682</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>394746; 445963</t>
+          <t>396633; 446845</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>481552; 528564</t>
+          <t>479648; 528575</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>767722; 896448</t>
+          <t>646259; 685323</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139089</t>
+          <t>152265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>318639</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>457728</t>
+          <t>499697</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61301; 88425</t>
+          <t>60325; 87654</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59955; 92019</t>
+          <t>62087; 92356</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83120; 111525</t>
+          <t>84116; 112529</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>125844; 151896</t>
+          <t>137584; 166606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>216445; 251653</t>
+          <t>215661; 250515</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>209290; 247960</t>
+          <t>208049; 249153</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>246712; 291810</t>
+          <t>247344; 290264</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>304700; 331225</t>
+          <t>334065; 362194</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>286101; 333948</t>
+          <t>283106; 332473</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>280658; 334460</t>
+          <t>280084; 333828</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>341061; 394782</t>
+          <t>340280; 393724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>438262; 477248</t>
+          <t>476679; 519632</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1064943; 1177799</t>
+          <t>1064692; 1178098</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1437310; 1559799</t>
+          <t>1437562; 1557613</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1734100; 1856067</t>
+          <t>1732899; 1853887</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1616269; 2302431</t>
+          <t>2251481; 2374350</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2791090; 2877241</t>
+          <t>2796494; 2881418</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2926098; 3019903</t>
+          <t>2923419; 3017987</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3051482; 3135285</t>
+          <t>3055023; 3134357</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3353826; 3455773</t>
+          <t>3345644; 3421280</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3878149; 4043597</t>
+          <t>3879112; 4037308</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4386140; 4552176</t>
+          <t>4385240; 4552131</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4816483; 4963963</t>
+          <t>4818389; 4971138</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4883769; 5758566</t>
+          <t>5618246; 5775071</t>
         </is>
       </c>
     </row>
